--- a/Tensile_Strength_WI2026.xlsx
+++ b/Tensile_Strength_WI2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/stn424_ads_northwestern_edu/Documents/Collaborations/Proposals/GO-Barrier, TFMI Proposals with Tim Wei/URAP_2023-10/Shared/Lanning, Mackenzie/Mechanical Strength Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/stn424_ads_northwestern_edu/Documents/Collaborations/Proposals/GO-Barrier, TFMI Proposals with Tim Wei/URAP_2023-10/Shared/Lanning, Mackenzie/graphene-oxide-paper-coatings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1058" documentId="8_{7B2FAAB4-C99F-BB44-A2F6-F39A6A1F9A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1640DF3-C001-E148-996A-37AA54FB8AF1}"/>
+  <xr:revisionPtr revIDLastSave="1097" documentId="8_{7B2FAAB4-C99F-BB44-A2F6-F39A6A1F9A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4427C3E-ACCE-9D49-835B-FABE49456B48}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="740" windowWidth="25980" windowHeight="17180" activeTab="2" xr2:uid="{015A8FDE-A9B3-2147-A675-FAFDB19A3A65}"/>
+    <workbookView minimized="1" xWindow="3420" yWindow="740" windowWidth="25980" windowHeight="17180" activeTab="1" xr2:uid="{015A8FDE-A9B3-2147-A675-FAFDB19A3A65}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="37">
   <si>
     <t>Sample</t>
   </si>
@@ -143,6 +143,12 @@
   </si>
   <si>
     <t>5% WBBC + 0.1% GO</t>
+  </si>
+  <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>Metsa</t>
   </si>
 </sst>
 </file>
@@ -5673,7 +5679,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED6813D-87D4-2740-A82B-F292F774EA67}">
-  <dimension ref="A1:I210"/>
+  <dimension ref="A1:K230"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -10161,7 +10167,7 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A209" s="3">
         <v>9</v>
       </c>
@@ -10181,7 +10187,7 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A210" s="3">
         <v>10</v>
       </c>
@@ -10207,6 +10213,302 @@
       <c r="I210">
         <f>STDEV(E201:E210)</f>
         <v>2.2568414506414349</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A211" s="3">
+        <v>1</v>
+      </c>
+      <c r="B211" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C211" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D211">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A212" s="3">
+        <v>2</v>
+      </c>
+      <c r="B212" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C212" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D212">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A213" s="3">
+        <v>3</v>
+      </c>
+      <c r="B213" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C213" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D213">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A214" s="3">
+        <v>4</v>
+      </c>
+      <c r="B214" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C214" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D214">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A215" s="3">
+        <v>5</v>
+      </c>
+      <c r="B215" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C215" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D215">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A216" s="3">
+        <v>6</v>
+      </c>
+      <c r="B216" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C216" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D216">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A217" s="3">
+        <v>7</v>
+      </c>
+      <c r="B217" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C217" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D217">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A218" s="3">
+        <v>8</v>
+      </c>
+      <c r="B218" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C218" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D218">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A219" s="3">
+        <v>9</v>
+      </c>
+      <c r="B219" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C219" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D219">
+        <v>0.37</v>
+      </c>
+      <c r="J219">
+        <f>AVERAGE(D211:D220)</f>
+        <v>0.36899999999999999</v>
+      </c>
+      <c r="K219">
+        <f>STDEV(D211:D220)</f>
+        <v>7.3786478737262262E-3</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A220" s="3">
+        <v>10</v>
+      </c>
+      <c r="B220" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C220" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D220">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A221" s="3">
+        <v>1</v>
+      </c>
+      <c r="B221" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C221" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D221">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A222" s="3">
+        <v>2</v>
+      </c>
+      <c r="B222" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C222" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D222">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A223" s="3">
+        <v>3</v>
+      </c>
+      <c r="B223" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C223" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D223">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A224" s="3">
+        <v>4</v>
+      </c>
+      <c r="B224" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C224" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D224">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A225" s="3">
+        <v>5</v>
+      </c>
+      <c r="B225" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C225" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D225">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A226" s="3">
+        <v>6</v>
+      </c>
+      <c r="B226" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C226" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D226">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A227" s="3">
+        <v>7</v>
+      </c>
+      <c r="B227" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C227" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D227">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A228" s="3">
+        <v>8</v>
+      </c>
+      <c r="B228" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C228" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D228">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A229" s="3">
+        <v>9</v>
+      </c>
+      <c r="B229" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C229" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D229">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A230" s="3">
+        <v>10</v>
+      </c>
+      <c r="B230" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C230" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D230">
+        <v>0.42</v>
+      </c>
+      <c r="J230">
+        <f>AVERAGE(D221:D230)</f>
+        <v>0.40599999999999997</v>
+      </c>
+      <c r="K230">
+        <f>STDEV(D221:D230)</f>
+        <v>6.9920589878009901E-3</v>
       </c>
     </row>
   </sheetData>

--- a/Tensile_Strength_WI2026.xlsx
+++ b/Tensile_Strength_WI2026.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1097" documentId="8_{7B2FAAB4-C99F-BB44-A2F6-F39A6A1F9A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4427C3E-ACCE-9D49-835B-FABE49456B48}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3420" yWindow="740" windowWidth="25980" windowHeight="17180" activeTab="1" xr2:uid="{015A8FDE-A9B3-2147-A675-FAFDB19A3A65}"/>
+    <workbookView xWindow="3420" yWindow="740" windowWidth="25980" windowHeight="17180" activeTab="1" xr2:uid="{015A8FDE-A9B3-2147-A675-FAFDB19A3A65}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>

--- a/Tensile_Strength_WI2026.xlsx
+++ b/Tensile_Strength_WI2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/stn424_ads_northwestern_edu/Documents/Collaborations/Proposals/GO-Barrier, TFMI Proposals with Tim Wei/URAP_2023-10/Shared/Lanning, Mackenzie/graphene-oxide-paper-coatings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1097" documentId="8_{7B2FAAB4-C99F-BB44-A2F6-F39A6A1F9A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4427C3E-ACCE-9D49-835B-FABE49456B48}"/>
+  <xr:revisionPtr revIDLastSave="1102" documentId="8_{7B2FAAB4-C99F-BB44-A2F6-F39A6A1F9A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{219E75DD-7686-6340-8D47-B493B2441685}"/>
   <bookViews>
     <workbookView xWindow="3420" yWindow="740" windowWidth="25980" windowHeight="17180" activeTab="1" xr2:uid="{015A8FDE-A9B3-2147-A675-FAFDB19A3A65}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="37">
   <si>
     <t>Sample</t>
   </si>
@@ -5684,12 +5684,13 @@
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="22.83203125" customWidth="1"/>
     <col min="7" max="7" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5700,15 +5701,12 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H1" s="2" t="s">
@@ -5729,15 +5727,12 @@
         <v>22</v>
       </c>
       <c r="D2" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E2" s="8">
         <v>59.6</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="11">
+      <c r="F2" s="11">
         <v>46059</v>
       </c>
     </row>
@@ -5752,15 +5747,12 @@
         <v>22</v>
       </c>
       <c r="D3" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E3" s="8">
         <v>62.5</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="11">
+      <c r="F3" s="11">
         <v>46059</v>
       </c>
     </row>
@@ -5775,15 +5767,12 @@
         <v>22</v>
       </c>
       <c r="D4" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E4" s="8">
         <v>63.7</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="11">
+      <c r="F4" s="11">
         <v>46059</v>
       </c>
     </row>
@@ -5798,15 +5787,12 @@
         <v>22</v>
       </c>
       <c r="D5" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E5" s="8">
         <v>58.6</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="E5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="11">
+      <c r="F5" s="11">
         <v>46059</v>
       </c>
     </row>
@@ -5821,15 +5807,12 @@
         <v>22</v>
       </c>
       <c r="D6" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E6" s="8">
         <v>62.8</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="E6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="11">
+      <c r="F6" s="11">
         <v>46059</v>
       </c>
     </row>
@@ -5844,15 +5827,12 @@
         <v>22</v>
       </c>
       <c r="D7" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E7" s="8">
         <v>57.6</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="E7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="11">
+      <c r="F7" s="11">
         <v>46059</v>
       </c>
     </row>
@@ -5867,15 +5847,12 @@
         <v>22</v>
       </c>
       <c r="D8" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E8" s="8">
         <v>57.7</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="11">
+      <c r="F8" s="11">
         <v>46059</v>
       </c>
     </row>
@@ -5890,15 +5867,12 @@
         <v>22</v>
       </c>
       <c r="D9" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E9" s="8">
         <v>56.6</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="E9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="11">
+      <c r="F9" s="11">
         <v>46059</v>
       </c>
     </row>
@@ -5913,15 +5887,12 @@
         <v>22</v>
       </c>
       <c r="D10" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E10" s="8">
         <v>61.2</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="E10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="11">
+      <c r="F10" s="11">
         <v>46059</v>
       </c>
     </row>
@@ -5936,23 +5907,20 @@
         <v>22</v>
       </c>
       <c r="D11" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E11" s="8">
         <v>62.4</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="E11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="11">
+      <c r="F11" s="11">
         <v>46059</v>
       </c>
       <c r="H11">
-        <f>AVERAGE(E2:E11)</f>
+        <f>AVERAGE(D2:D11)</f>
         <v>60.27</v>
       </c>
       <c r="I11">
-        <f>STDEV(E2:E11)</f>
+        <f>STDEV(D2:D11)</f>
         <v>2.5599696178752671</v>
       </c>
     </row>
@@ -5967,15 +5935,12 @@
         <v>22</v>
       </c>
       <c r="D12" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E12" s="8">
         <v>30.7</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" s="11">
+      <c r="E12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="11">
         <v>46059</v>
       </c>
     </row>
@@ -5990,15 +5955,12 @@
         <v>22</v>
       </c>
       <c r="D13" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E13" s="8">
         <v>32.799999999999997</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="11">
+      <c r="E13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="11">
         <v>46059</v>
       </c>
     </row>
@@ -6013,15 +5975,12 @@
         <v>22</v>
       </c>
       <c r="D14" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E14" s="8">
         <v>29.5</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" s="11">
+      <c r="E14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="11">
         <v>46059</v>
       </c>
     </row>
@@ -6036,15 +5995,12 @@
         <v>22</v>
       </c>
       <c r="D15" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E15" s="8">
         <v>31.5</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" s="11">
+      <c r="E15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="11">
         <v>46059</v>
       </c>
     </row>
@@ -6059,15 +6015,12 @@
         <v>22</v>
       </c>
       <c r="D16" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E16" s="8">
         <v>31.2</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" s="11">
+      <c r="E16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="11">
         <v>46059</v>
       </c>
     </row>
@@ -6082,15 +6035,12 @@
         <v>22</v>
       </c>
       <c r="D17" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E17" s="8">
         <v>29.6</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="11">
+      <c r="E17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="11">
         <v>46059</v>
       </c>
     </row>
@@ -6105,15 +6055,12 @@
         <v>22</v>
       </c>
       <c r="D18" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E18" s="8">
         <v>33.6</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" s="11">
+      <c r="E18" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="11">
         <v>46059</v>
       </c>
     </row>
@@ -6128,15 +6075,12 @@
         <v>22</v>
       </c>
       <c r="D19" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E19" s="8">
         <v>31.5</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G19" s="11">
+      <c r="E19" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="11">
         <v>46059</v>
       </c>
     </row>
@@ -6151,15 +6095,12 @@
         <v>22</v>
       </c>
       <c r="D20" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E20" s="8">
         <v>27.4</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G20" s="11">
+      <c r="E20" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="11">
         <v>46059</v>
       </c>
     </row>
@@ -6174,23 +6115,20 @@
         <v>22</v>
       </c>
       <c r="D21" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E21" s="8">
         <v>29.8</v>
       </c>
-      <c r="F21" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G21" s="11">
+      <c r="E21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="11">
         <v>46059</v>
       </c>
       <c r="H21">
-        <f>AVERAGE(E12:E21)</f>
+        <f>AVERAGE(D12:D21)</f>
         <v>30.759999999999998</v>
       </c>
       <c r="I21">
-        <f>STDEV(E12:E21)</f>
+        <f>STDEV(D12:D21)</f>
         <v>1.7846256999407155</v>
       </c>
     </row>
@@ -6205,15 +6143,12 @@
         <v>25</v>
       </c>
       <c r="D22" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E22" s="8">
         <v>53.3</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="E22" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G22" s="11">
+      <c r="F22" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6228,15 +6163,12 @@
         <v>25</v>
       </c>
       <c r="D23" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E23" s="8">
         <v>57.2</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="E23" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G23" s="11">
+      <c r="F23" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6251,15 +6183,12 @@
         <v>25</v>
       </c>
       <c r="D24" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="E24" s="8">
         <v>52</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="E24" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G24" s="11">
+      <c r="F24" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6274,15 +6203,12 @@
         <v>25</v>
       </c>
       <c r="D25" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="E25" s="8">
         <v>51.9</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="E25" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G25" s="11">
+      <c r="F25" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6297,15 +6223,12 @@
         <v>25</v>
       </c>
       <c r="D26" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E26" s="8">
         <v>44</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="E26" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G26" s="11">
+      <c r="F26" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6320,15 +6243,12 @@
         <v>25</v>
       </c>
       <c r="D27" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E27" s="8">
         <v>56.8</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="E27" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G27" s="11">
+      <c r="F27" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6343,15 +6263,12 @@
         <v>25</v>
       </c>
       <c r="D28" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E28" s="8">
         <v>54.8</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="E28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G28" s="11">
+      <c r="F28" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6366,15 +6283,12 @@
         <v>25</v>
       </c>
       <c r="D29" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E29" s="8">
         <v>46.4</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="E29" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G29" s="11">
+      <c r="F29" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6389,15 +6303,12 @@
         <v>25</v>
       </c>
       <c r="D30" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="E30" s="8">
         <v>52.2</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="E30" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G30" s="11">
+      <c r="F30" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6412,23 +6323,20 @@
         <v>25</v>
       </c>
       <c r="D31" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E31" s="8">
         <v>49.7</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="E31" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G31" s="11">
+      <c r="F31" s="11">
         <v>46062</v>
       </c>
       <c r="H31">
-        <f>AVERAGE(E22:E31)</f>
+        <f>AVERAGE(D22:D31)</f>
         <v>51.83</v>
       </c>
       <c r="I31">
-        <f>STDEV(E22:E31)</f>
+        <f>STDEV(D22:D31)</f>
         <v>4.216646903774504</v>
       </c>
     </row>
@@ -6442,13 +6350,13 @@
       <c r="C32" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E32" s="8">
+      <c r="D32" s="8">
         <v>20.100000000000001</v>
       </c>
-      <c r="F32" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G32" s="11">
+      <c r="E32" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="11">
         <v>46080</v>
       </c>
     </row>
@@ -6462,13 +6370,13 @@
       <c r="C33" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E33" s="8">
+      <c r="D33" s="8">
         <v>23.2</v>
       </c>
-      <c r="F33" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G33" s="11">
+      <c r="E33" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" s="11">
         <v>46080</v>
       </c>
     </row>
@@ -6482,13 +6390,13 @@
       <c r="C34" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E34" s="8">
+      <c r="D34" s="8">
         <v>25.5</v>
       </c>
-      <c r="F34" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G34" s="11">
+      <c r="E34" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" s="11">
         <v>46080</v>
       </c>
     </row>
@@ -6502,13 +6410,13 @@
       <c r="C35" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E35" s="8">
+      <c r="D35" s="8">
         <v>24.6</v>
       </c>
-      <c r="F35" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G35" s="11">
+      <c r="E35" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" s="11">
         <v>46080</v>
       </c>
     </row>
@@ -6522,13 +6430,13 @@
       <c r="C36" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E36" s="8">
+      <c r="D36" s="8">
         <v>21.2</v>
       </c>
-      <c r="F36" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G36" s="11">
+      <c r="E36" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" s="11">
         <v>46080</v>
       </c>
     </row>
@@ -6542,13 +6450,13 @@
       <c r="C37" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E37" s="8">
+      <c r="D37" s="8">
         <v>24.1</v>
       </c>
-      <c r="F37" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G37" s="11">
+      <c r="E37" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" s="11">
         <v>46080</v>
       </c>
     </row>
@@ -6562,13 +6470,13 @@
       <c r="C38" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E38" s="8">
+      <c r="D38" s="8">
         <v>21.6</v>
       </c>
-      <c r="F38" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G38" s="11">
+      <c r="E38" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F38" s="11">
         <v>46080</v>
       </c>
     </row>
@@ -6582,13 +6490,13 @@
       <c r="C39" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E39" s="8">
+      <c r="D39" s="8">
         <v>20.5</v>
       </c>
-      <c r="F39" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G39" s="11">
+      <c r="E39" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" s="11">
         <v>46080</v>
       </c>
     </row>
@@ -6602,13 +6510,13 @@
       <c r="C40" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E40" s="8">
+      <c r="D40" s="8">
         <v>24.6</v>
       </c>
-      <c r="F40" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G40" s="11">
+      <c r="E40" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" s="11">
         <v>46080</v>
       </c>
     </row>
@@ -6622,21 +6530,21 @@
       <c r="C41" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E41" s="8">
+      <c r="D41" s="8">
         <v>22.2</v>
       </c>
-      <c r="F41" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G41" s="11">
+      <c r="E41" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F41" s="11">
         <v>46080</v>
       </c>
       <c r="H41">
-        <f>AVERAGE(E32:E41)</f>
+        <f>AVERAGE(D32:D41)</f>
         <v>22.759999999999998</v>
       </c>
       <c r="I41">
-        <f>STDEV(E32:E41)</f>
+        <f>STDEV(D32:D41)</f>
         <v>1.9015782918407542</v>
       </c>
     </row>
@@ -6651,15 +6559,12 @@
         <v>17</v>
       </c>
       <c r="D42" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="E42" s="8">
         <v>58</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="E42" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G42" s="11">
+      <c r="F42" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6674,15 +6579,12 @@
         <v>17</v>
       </c>
       <c r="D43" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="E43" s="8">
         <v>58.1</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="E43" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G43" s="11">
+      <c r="F43" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6697,15 +6599,12 @@
         <v>17</v>
       </c>
       <c r="D44" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E44" s="8">
         <v>55.7</v>
       </c>
-      <c r="F44" s="8" t="s">
+      <c r="E44" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G44" s="11">
+      <c r="F44" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6720,15 +6619,12 @@
         <v>17</v>
       </c>
       <c r="D45" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="E45" s="8">
         <v>54.7</v>
       </c>
-      <c r="F45" s="8" t="s">
+      <c r="E45" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G45" s="11">
+      <c r="F45" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6743,15 +6639,12 @@
         <v>17</v>
       </c>
       <c r="D46" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="E46" s="8">
         <v>56.6</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="E46" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G46" s="11">
+      <c r="F46" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6766,15 +6659,12 @@
         <v>17</v>
       </c>
       <c r="D47" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="E47" s="8">
         <v>60.1</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="E47" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G47" s="11">
+      <c r="F47" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6789,15 +6679,12 @@
         <v>17</v>
       </c>
       <c r="D48" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="E48" s="8">
         <v>62.2</v>
       </c>
-      <c r="F48" s="8" t="s">
+      <c r="E48" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G48" s="11">
+      <c r="F48" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6812,15 +6699,12 @@
         <v>17</v>
       </c>
       <c r="D49" s="8">
-        <v>0.16</v>
-      </c>
-      <c r="E49" s="8">
         <v>57.3</v>
       </c>
-      <c r="F49" s="8" t="s">
+      <c r="E49" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G49" s="11">
+      <c r="F49" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6835,15 +6719,12 @@
         <v>17</v>
       </c>
       <c r="D50" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E50" s="8">
         <v>56.7</v>
       </c>
-      <c r="F50" s="8" t="s">
+      <c r="E50" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G50" s="11">
+      <c r="F50" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6858,23 +6739,20 @@
         <v>17</v>
       </c>
       <c r="D51" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="E51" s="8">
         <v>57</v>
       </c>
-      <c r="F51" s="8" t="s">
+      <c r="E51" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G51" s="11">
+      <c r="F51" s="11">
         <v>46062</v>
       </c>
       <c r="H51">
-        <f>AVERAGE(E42:E51)</f>
+        <f>AVERAGE(D42:D51)</f>
         <v>57.640000000000008</v>
       </c>
       <c r="I51">
-        <f>STDEV(E42:E51)</f>
+        <f>STDEV(D42:D51)</f>
         <v>2.1624060673240817</v>
       </c>
     </row>
@@ -6889,15 +6767,12 @@
         <v>17</v>
       </c>
       <c r="D52" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="E52" s="8">
         <v>28</v>
       </c>
-      <c r="F52" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G52" s="11">
+      <c r="E52" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F52" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6912,15 +6787,12 @@
         <v>17</v>
       </c>
       <c r="D53" s="8">
-        <v>0.16</v>
-      </c>
-      <c r="E53" s="8">
         <v>29.3</v>
       </c>
-      <c r="F53" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G53" s="11">
+      <c r="E53" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F53" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6935,15 +6807,12 @@
         <v>17</v>
       </c>
       <c r="D54" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="E54" s="8">
         <v>28.2</v>
       </c>
-      <c r="F54" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G54" s="11">
+      <c r="E54" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F54" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6958,15 +6827,12 @@
         <v>17</v>
       </c>
       <c r="D55" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="E55" s="8">
         <v>27.8</v>
       </c>
-      <c r="F55" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G55" s="11">
+      <c r="E55" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F55" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -6981,15 +6847,12 @@
         <v>17</v>
       </c>
       <c r="D56" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="E56" s="8">
         <v>28.3</v>
       </c>
-      <c r="F56" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G56" s="11">
+      <c r="E56" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F56" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -7004,15 +6867,12 @@
         <v>17</v>
       </c>
       <c r="D57" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="E57" s="8">
         <v>29</v>
       </c>
-      <c r="F57" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G57" s="11">
+      <c r="E57" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F57" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -7027,15 +6887,12 @@
         <v>17</v>
       </c>
       <c r="D58" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="E58" s="8">
         <v>28.2</v>
       </c>
-      <c r="F58" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G58" s="11">
+      <c r="E58" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F58" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -7050,15 +6907,12 @@
         <v>17</v>
       </c>
       <c r="D59" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="E59" s="8">
         <v>27.8</v>
       </c>
-      <c r="F59" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G59" s="11">
+      <c r="E59" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F59" s="11">
         <v>46062</v>
       </c>
     </row>
@@ -7073,23 +6927,20 @@
         <v>17</v>
       </c>
       <c r="D60" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="E60" s="8">
         <v>28.3</v>
       </c>
-      <c r="F60" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G60" s="11">
+      <c r="E60" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F60" s="11">
         <v>46062</v>
       </c>
       <c r="H60">
-        <f>AVERAGE(E52:E60)</f>
+        <f>AVERAGE(D52:D60)</f>
         <v>28.322222222222223</v>
       </c>
       <c r="I60">
-        <f>STDEV(E52:E60)</f>
+        <f>STDEV(D52:D60)</f>
         <v>0.51180508442613626</v>
       </c>
     </row>
@@ -7103,14 +6954,13 @@
       <c r="C61" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8">
+      <c r="D61" s="8">
         <v>56.9</v>
       </c>
-      <c r="F61" s="8" t="s">
+      <c r="E61" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G61" s="11">
+      <c r="F61" s="11">
         <v>46064</v>
       </c>
     </row>
@@ -7124,14 +6974,13 @@
       <c r="C62" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8">
+      <c r="D62" s="8">
         <v>55.8</v>
       </c>
-      <c r="F62" s="8" t="s">
+      <c r="E62" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G62" s="11">
+      <c r="F62" s="11">
         <v>46064</v>
       </c>
     </row>
@@ -7145,13 +6994,13 @@
       <c r="C63" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E63" s="8">
+      <c r="D63" s="8">
         <v>64.3</v>
       </c>
-      <c r="F63" s="8" t="s">
+      <c r="E63" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G63" s="11">
+      <c r="F63" s="11">
         <v>46064</v>
       </c>
     </row>
@@ -7165,13 +7014,13 @@
       <c r="C64" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E64" s="8">
+      <c r="D64" s="8">
         <v>58.2</v>
       </c>
-      <c r="F64" s="8" t="s">
+      <c r="E64" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G64" s="11">
+      <c r="F64" s="11">
         <v>46064</v>
       </c>
     </row>
@@ -7185,13 +7034,13 @@
       <c r="C65" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E65" s="8">
+      <c r="D65" s="8">
         <v>62.1</v>
       </c>
-      <c r="F65" s="8" t="s">
+      <c r="E65" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G65" s="11">
+      <c r="F65" s="11">
         <v>46064</v>
       </c>
     </row>
@@ -7205,13 +7054,13 @@
       <c r="C66" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E66" s="8">
+      <c r="D66" s="8">
         <v>58.6</v>
       </c>
-      <c r="F66" s="8" t="s">
+      <c r="E66" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G66" s="11">
+      <c r="F66" s="11">
         <v>46064</v>
       </c>
     </row>
@@ -7225,13 +7074,13 @@
       <c r="C67" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E67" s="8">
+      <c r="D67" s="8">
         <v>57.9</v>
       </c>
-      <c r="F67" s="8" t="s">
+      <c r="E67" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G67" s="11">
+      <c r="F67" s="11">
         <v>46064</v>
       </c>
     </row>
@@ -7245,13 +7094,13 @@
       <c r="C68" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E68" s="8">
+      <c r="D68" s="8">
         <v>60.3</v>
       </c>
-      <c r="F68" s="8" t="s">
+      <c r="E68" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G68" s="11">
+      <c r="F68" s="11">
         <v>46064</v>
       </c>
     </row>
@@ -7265,13 +7114,13 @@
       <c r="C69" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E69" s="8">
+      <c r="D69" s="8">
         <v>58.6</v>
       </c>
-      <c r="F69" s="8" t="s">
+      <c r="E69" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G69" s="11">
+      <c r="F69" s="11">
         <v>46064</v>
       </c>
     </row>
@@ -7285,21 +7134,21 @@
       <c r="C70" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E70" s="8">
+      <c r="D70" s="8">
         <v>58.3</v>
       </c>
-      <c r="F70" s="8" t="s">
+      <c r="E70" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G70" s="11">
+      <c r="F70" s="11">
         <v>46064</v>
       </c>
       <c r="H70">
-        <f>AVERAGE(E61:E70)</f>
+        <f>AVERAGE(D61:D70)</f>
         <v>59.1</v>
       </c>
       <c r="I70">
-        <f>STDEV(E61:E70)</f>
+        <f>STDEV(D61:D70)</f>
         <v>2.5077657165072034</v>
       </c>
     </row>
@@ -7313,13 +7162,13 @@
       <c r="C71" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E71" s="8">
+      <c r="D71" s="8">
         <v>28</v>
       </c>
-      <c r="F71" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G71" s="11">
+      <c r="E71" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F71" s="11">
         <v>46064</v>
       </c>
     </row>
@@ -7333,13 +7182,13 @@
       <c r="C72" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E72" s="8">
+      <c r="D72" s="8">
         <v>30.9</v>
       </c>
-      <c r="F72" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G72" s="11">
+      <c r="E72" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F72" s="11">
         <v>46064</v>
       </c>
     </row>
@@ -7353,13 +7202,13 @@
       <c r="C73" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E73" s="8">
+      <c r="D73" s="8">
         <v>27.2</v>
       </c>
-      <c r="F73" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G73" s="11">
+      <c r="E73" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F73" s="11">
         <v>46064</v>
       </c>
     </row>
@@ -7373,13 +7222,13 @@
       <c r="C74" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E74" s="8">
+      <c r="D74" s="8">
         <v>28.4</v>
       </c>
-      <c r="F74" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G74" s="11">
+      <c r="E74" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F74" s="11">
         <v>46064</v>
       </c>
     </row>
@@ -7393,13 +7242,13 @@
       <c r="C75" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E75" s="8">
+      <c r="D75" s="8">
         <v>29</v>
       </c>
-      <c r="F75" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G75" s="11">
+      <c r="E75" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F75" s="11">
         <v>46064</v>
       </c>
     </row>
@@ -7413,13 +7262,13 @@
       <c r="C76" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E76" s="8">
+      <c r="D76" s="8">
         <v>27.5</v>
       </c>
-      <c r="F76" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G76" s="11">
+      <c r="E76" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F76" s="11">
         <v>46064</v>
       </c>
     </row>
@@ -7433,13 +7282,13 @@
       <c r="C77" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E77" s="8">
+      <c r="D77" s="8">
         <v>29.9</v>
       </c>
-      <c r="F77" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G77" s="11">
+      <c r="E77" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F77" s="11">
         <v>46064</v>
       </c>
     </row>
@@ -7453,13 +7302,13 @@
       <c r="C78" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E78" s="8">
+      <c r="D78" s="8">
         <v>27.4</v>
       </c>
-      <c r="F78" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G78" s="11">
+      <c r="E78" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F78" s="11">
         <v>46064</v>
       </c>
     </row>
@@ -7473,13 +7322,13 @@
       <c r="C79" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E79" s="8">
+      <c r="D79" s="8">
         <v>28.1</v>
       </c>
-      <c r="F79" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G79" s="11">
+      <c r="E79" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F79" s="11">
         <v>46064</v>
       </c>
     </row>
@@ -7493,21 +7342,21 @@
       <c r="C80" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E80" s="8">
+      <c r="D80" s="8">
         <v>27.9</v>
       </c>
-      <c r="F80" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G80" s="11">
+      <c r="E80" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F80" s="11">
         <v>46064</v>
       </c>
       <c r="H80">
-        <f>AVERAGE(E71:E80)</f>
+        <f>AVERAGE(D71:D80)</f>
         <v>28.43</v>
       </c>
       <c r="I80">
-        <f>STDEV(E71:E80)</f>
+        <f>STDEV(D71:D80)</f>
         <v>1.1832629087025039</v>
       </c>
     </row>
@@ -7521,13 +7370,13 @@
       <c r="C81" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E81" s="8">
+      <c r="D81" s="8">
         <v>52.8</v>
       </c>
-      <c r="F81" s="8" t="s">
+      <c r="E81" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G81" s="11">
+      <c r="F81" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7541,13 +7390,13 @@
       <c r="C82" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E82" s="8">
+      <c r="D82" s="8">
         <v>54.7</v>
       </c>
-      <c r="F82" s="8" t="s">
+      <c r="E82" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G82" s="11">
+      <c r="F82" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7561,13 +7410,13 @@
       <c r="C83" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E83" s="8">
+      <c r="D83" s="8">
         <v>53</v>
       </c>
-      <c r="F83" s="8" t="s">
+      <c r="E83" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G83" s="11">
+      <c r="F83" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7581,13 +7430,13 @@
       <c r="C84" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E84" s="8">
+      <c r="D84" s="8">
         <v>52.8</v>
       </c>
-      <c r="F84" s="8" t="s">
+      <c r="E84" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G84" s="11">
+      <c r="F84" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7601,13 +7450,13 @@
       <c r="C85" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E85" s="8">
+      <c r="D85" s="8">
         <v>51.1</v>
       </c>
-      <c r="F85" s="8" t="s">
+      <c r="E85" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G85" s="11">
+      <c r="F85" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7621,13 +7470,13 @@
       <c r="C86" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E86" s="8">
+      <c r="D86" s="8">
         <v>53.5</v>
       </c>
-      <c r="F86" s="8" t="s">
+      <c r="E86" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G86" s="11">
+      <c r="F86" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7641,13 +7490,13 @@
       <c r="C87" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E87" s="8">
+      <c r="D87" s="8">
         <v>52.4</v>
       </c>
-      <c r="F87" s="8" t="s">
+      <c r="E87" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G87" s="11">
+      <c r="F87" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7661,13 +7510,13 @@
       <c r="C88" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E88" s="8">
+      <c r="D88" s="8">
         <v>50.8</v>
       </c>
-      <c r="F88" s="8" t="s">
+      <c r="E88" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G88" s="11">
+      <c r="F88" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7681,13 +7530,13 @@
       <c r="C89" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E89" s="8">
+      <c r="D89" s="8">
         <v>53.1</v>
       </c>
-      <c r="F89" s="8" t="s">
+      <c r="E89" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G89" s="11">
+      <c r="F89" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7701,21 +7550,21 @@
       <c r="C90" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E90" s="8">
+      <c r="D90" s="8">
         <v>52.4</v>
       </c>
-      <c r="F90" s="8" t="s">
+      <c r="E90" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G90" s="11">
+      <c r="F90" s="11">
         <v>46070</v>
       </c>
       <c r="H90">
-        <f>AVERAGE(E81:E90)</f>
+        <f>AVERAGE(D81:D90)</f>
         <v>52.660000000000004</v>
       </c>
       <c r="I90">
-        <f>STDEV(E81:E90)</f>
+        <f>STDEV(D81:D90)</f>
         <v>1.1177358065899721</v>
       </c>
     </row>
@@ -7729,13 +7578,13 @@
       <c r="C91" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E91" s="8">
+      <c r="D91" s="8">
         <v>27</v>
       </c>
-      <c r="F91" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G91" s="11">
+      <c r="E91" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F91" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7749,13 +7598,13 @@
       <c r="C92" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E92" s="8">
+      <c r="D92" s="8">
         <v>30.6</v>
       </c>
-      <c r="F92" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G92" s="11">
+      <c r="E92" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F92" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7769,13 +7618,13 @@
       <c r="C93" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E93" s="8">
+      <c r="D93" s="8">
         <v>27.1</v>
       </c>
-      <c r="F93" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G93" s="11">
+      <c r="E93" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F93" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7789,13 +7638,13 @@
       <c r="C94" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E94" s="8">
+      <c r="D94" s="8">
         <v>27.6</v>
       </c>
-      <c r="F94" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G94" s="11">
+      <c r="E94" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F94" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7809,13 +7658,13 @@
       <c r="C95" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E95" s="8">
+      <c r="D95" s="8">
         <v>27.9</v>
       </c>
-      <c r="F95" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G95" s="11">
+      <c r="E95" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F95" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7829,13 +7678,13 @@
       <c r="C96" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E96" s="8">
+      <c r="D96" s="8">
         <v>29.8</v>
       </c>
-      <c r="F96" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G96" s="11">
+      <c r="E96" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F96" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7849,13 +7698,13 @@
       <c r="C97" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E97" s="8">
+      <c r="D97" s="8">
         <v>31.3</v>
       </c>
-      <c r="F97" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G97" s="11">
+      <c r="E97" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F97" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7869,13 +7718,13 @@
       <c r="C98" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E98" s="8">
+      <c r="D98" s="8">
         <v>28.9</v>
       </c>
-      <c r="F98" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G98" s="11">
+      <c r="E98" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F98" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7889,13 +7738,13 @@
       <c r="C99" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E99" s="8">
+      <c r="D99" s="8">
         <v>26.9</v>
       </c>
-      <c r="F99" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G99" s="11">
+      <c r="E99" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F99" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7909,21 +7758,21 @@
       <c r="C100" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E100" s="8">
+      <c r="D100" s="8">
         <v>29.5</v>
       </c>
-      <c r="F100" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G100" s="11">
+      <c r="E100" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F100" s="11">
         <v>46070</v>
       </c>
       <c r="H100">
-        <f>AVERAGE(E91:E100)</f>
+        <f>AVERAGE(D91:D100)</f>
         <v>28.660000000000004</v>
       </c>
       <c r="I100">
-        <f>STDEV(E91:E100)</f>
+        <f>STDEV(D91:D100)</f>
         <v>1.5910862816188054</v>
       </c>
     </row>
@@ -7937,13 +7786,13 @@
       <c r="C101" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E101" s="8">
+      <c r="D101" s="8">
         <v>54.2</v>
       </c>
-      <c r="F101" s="8" t="s">
+      <c r="E101" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G101" s="11">
+      <c r="F101" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7957,13 +7806,13 @@
       <c r="C102" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E102" s="8">
+      <c r="D102" s="8">
         <v>54.3</v>
       </c>
-      <c r="F102" s="8" t="s">
+      <c r="E102" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G102" s="11">
+      <c r="F102" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7977,13 +7826,13 @@
       <c r="C103" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E103" s="8">
+      <c r="D103" s="8">
         <v>53.2</v>
       </c>
-      <c r="F103" s="8" t="s">
+      <c r="E103" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G103" s="11">
+      <c r="F103" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -7997,13 +7846,13 @@
       <c r="C104" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E104" s="8">
+      <c r="D104" s="8">
         <v>53.4</v>
       </c>
-      <c r="F104" s="8" t="s">
+      <c r="E104" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G104" s="11">
+      <c r="F104" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -8017,13 +7866,13 @@
       <c r="C105" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E105" s="8">
+      <c r="D105" s="8">
         <v>57.4</v>
       </c>
-      <c r="F105" s="8" t="s">
+      <c r="E105" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G105" s="11">
+      <c r="F105" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -8037,13 +7886,13 @@
       <c r="C106" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E106" s="8">
+      <c r="D106" s="8">
         <v>54.8</v>
       </c>
-      <c r="F106" s="8" t="s">
+      <c r="E106" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G106" s="11">
+      <c r="F106" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -8057,13 +7906,13 @@
       <c r="C107" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E107" s="8">
+      <c r="D107" s="8">
         <v>56.2</v>
       </c>
-      <c r="F107" s="8" t="s">
+      <c r="E107" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G107" s="11">
+      <c r="F107" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -8077,13 +7926,13 @@
       <c r="C108" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E108" s="8">
+      <c r="D108" s="8">
         <v>55.4</v>
       </c>
-      <c r="F108" s="8" t="s">
+      <c r="E108" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G108" s="11">
+      <c r="F108" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -8097,13 +7946,13 @@
       <c r="C109" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E109" s="8">
+      <c r="D109" s="8">
         <v>57</v>
       </c>
-      <c r="F109" s="8" t="s">
+      <c r="E109" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G109" s="11">
+      <c r="F109" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -8117,21 +7966,21 @@
       <c r="C110" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E110" s="8">
+      <c r="D110" s="8">
         <v>56.9</v>
       </c>
-      <c r="F110" s="8" t="s">
+      <c r="E110" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G110" s="11">
+      <c r="F110" s="11">
         <v>46070</v>
       </c>
       <c r="H110">
-        <f>AVERAGE(E101:E110)</f>
+        <f>AVERAGE(D101:D110)</f>
         <v>55.279999999999994</v>
       </c>
       <c r="I110">
-        <f>STDEV(E101:E110)</f>
+        <f>STDEV(D101:D110)</f>
         <v>1.5331883989473265</v>
       </c>
     </row>
@@ -8145,13 +7994,13 @@
       <c r="C111" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E111" s="8">
+      <c r="D111" s="8">
         <v>29.2</v>
       </c>
-      <c r="F111" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G111" s="11">
+      <c r="E111" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F111" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -8165,13 +8014,13 @@
       <c r="C112" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E112" s="8">
+      <c r="D112" s="8">
         <v>31.2</v>
       </c>
-      <c r="F112" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G112" s="11">
+      <c r="E112" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F112" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -8185,13 +8034,13 @@
       <c r="C113" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E113" s="8">
+      <c r="D113" s="8">
         <v>28.6</v>
       </c>
-      <c r="F113" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G113" s="11">
+      <c r="E113" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F113" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -8205,13 +8054,13 @@
       <c r="C114" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E114" s="8">
+      <c r="D114" s="8">
         <v>29</v>
       </c>
-      <c r="F114" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G114" s="11">
+      <c r="E114" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F114" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -8225,13 +8074,13 @@
       <c r="C115" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E115" s="8">
+      <c r="D115" s="8">
         <v>29.6</v>
       </c>
-      <c r="F115" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G115" s="11">
+      <c r="E115" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F115" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -8245,13 +8094,13 @@
       <c r="C116" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E116" s="8">
+      <c r="D116" s="8">
         <v>31.3</v>
       </c>
-      <c r="F116" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G116" s="11">
+      <c r="E116" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F116" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -8265,13 +8114,13 @@
       <c r="C117" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E117" s="8">
+      <c r="D117" s="8">
         <v>29.1</v>
       </c>
-      <c r="F117" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G117" s="11">
+      <c r="E117" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F117" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -8285,13 +8134,13 @@
       <c r="C118" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E118" s="8">
+      <c r="D118" s="8">
         <v>27.9</v>
       </c>
-      <c r="F118" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G118" s="11">
+      <c r="E118" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F118" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -8305,13 +8154,13 @@
       <c r="C119" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E119" s="8">
+      <c r="D119" s="8">
         <v>27.8</v>
       </c>
-      <c r="F119" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G119" s="11">
+      <c r="E119" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F119" s="11">
         <v>46070</v>
       </c>
     </row>
@@ -8325,21 +8174,21 @@
       <c r="C120" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E120" s="8">
+      <c r="D120" s="8">
         <v>29</v>
       </c>
-      <c r="F120" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G120" s="11">
+      <c r="E120" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F120" s="11">
         <v>46070</v>
       </c>
       <c r="H120">
-        <f>AVERAGE(E112:E120)</f>
+        <f>AVERAGE(D112:D120)</f>
         <v>29.277777777777779</v>
       </c>
       <c r="I120">
-        <f>STDEV(E112:E120)</f>
+        <f>STDEV(D112:D120)</f>
         <v>1.2557644860579729</v>
       </c>
     </row>
@@ -8353,13 +8202,13 @@
       <c r="C121" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E121" s="8">
+      <c r="D121" s="8">
         <v>32.200000000000003</v>
       </c>
-      <c r="F121" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G121" s="11">
+      <c r="E121" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F121" s="11">
         <v>46076</v>
       </c>
     </row>
@@ -8373,13 +8222,13 @@
       <c r="C122" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E122" s="8">
+      <c r="D122" s="8">
         <v>28.5</v>
       </c>
-      <c r="F122" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G122" s="11">
+      <c r="E122" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F122" s="11">
         <v>46076</v>
       </c>
     </row>
@@ -8393,13 +8242,13 @@
       <c r="C123" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E123" s="8">
+      <c r="D123" s="8">
         <v>29.6</v>
       </c>
-      <c r="F123" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G123" s="11">
+      <c r="E123" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F123" s="11">
         <v>46076</v>
       </c>
     </row>
@@ -8413,13 +8262,13 @@
       <c r="C124" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E124" s="8">
+      <c r="D124" s="8">
         <v>28.1</v>
       </c>
-      <c r="F124" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G124" s="11">
+      <c r="E124" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F124" s="11">
         <v>46076</v>
       </c>
     </row>
@@ -8433,13 +8282,13 @@
       <c r="C125" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E125" s="8">
+      <c r="D125" s="8">
         <v>28.5</v>
       </c>
-      <c r="F125" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G125" s="11">
+      <c r="E125" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F125" s="11">
         <v>46076</v>
       </c>
     </row>
@@ -8453,13 +8302,13 @@
       <c r="C126" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E126" s="8">
+      <c r="D126" s="8">
         <v>32.5</v>
       </c>
-      <c r="F126" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G126" s="11">
+      <c r="E126" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F126" s="11">
         <v>46076</v>
       </c>
     </row>
@@ -8473,13 +8322,13 @@
       <c r="C127" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E127" s="8">
+      <c r="D127" s="8">
         <v>32.200000000000003</v>
       </c>
-      <c r="F127" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G127" s="11">
+      <c r="E127" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F127" s="11">
         <v>46076</v>
       </c>
     </row>
@@ -8493,13 +8342,13 @@
       <c r="C128" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E128" s="8">
+      <c r="D128" s="8">
         <v>27.2</v>
       </c>
-      <c r="F128" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G128" s="11">
+      <c r="E128" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F128" s="11">
         <v>46076</v>
       </c>
     </row>
@@ -8513,13 +8362,13 @@
       <c r="C129" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E129" s="8">
+      <c r="D129" s="8">
         <v>29.8</v>
       </c>
-      <c r="F129" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G129" s="11">
+      <c r="E129" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F129" s="11">
         <v>46076</v>
       </c>
     </row>
@@ -8533,21 +8382,21 @@
       <c r="C130" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E130" s="8">
+      <c r="D130" s="8">
         <v>28.4</v>
       </c>
-      <c r="F130" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G130" s="11">
+      <c r="E130" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F130" s="11">
         <v>46076</v>
       </c>
       <c r="H130">
-        <f>AVERAGE(E121:E130)</f>
+        <f>AVERAGE(D121:D130)</f>
         <v>29.7</v>
       </c>
       <c r="I130">
-        <f>STDEV(E121:E130)</f>
+        <f>STDEV(D121:D130)</f>
         <v>1.9362047641943485</v>
       </c>
     </row>
@@ -8561,13 +8410,13 @@
       <c r="C131" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E131" s="8">
+      <c r="D131" s="8">
         <v>56.2</v>
       </c>
-      <c r="F131" s="8" t="s">
+      <c r="E131" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G131" s="11">
+      <c r="F131" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -8581,13 +8430,13 @@
       <c r="C132" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E132" s="8">
+      <c r="D132" s="8">
         <v>58.1</v>
       </c>
-      <c r="F132" s="8" t="s">
+      <c r="E132" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G132" s="11">
+      <c r="F132" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -8601,13 +8450,13 @@
       <c r="C133" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E133" s="8">
+      <c r="D133" s="8">
         <v>52.6</v>
       </c>
-      <c r="F133" s="8" t="s">
+      <c r="E133" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G133" s="11">
+      <c r="F133" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -8621,13 +8470,13 @@
       <c r="C134" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E134" s="8">
+      <c r="D134" s="8">
         <v>51</v>
       </c>
-      <c r="F134" s="8" t="s">
+      <c r="E134" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G134" s="11">
+      <c r="F134" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -8641,13 +8490,13 @@
       <c r="C135" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E135" s="8">
+      <c r="D135" s="8">
         <v>51.1</v>
       </c>
-      <c r="F135" s="8" t="s">
+      <c r="E135" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G135" s="11">
+      <c r="F135" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -8661,13 +8510,13 @@
       <c r="C136" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E136" s="8">
+      <c r="D136" s="8">
         <v>52.4</v>
       </c>
-      <c r="F136" s="8" t="s">
+      <c r="E136" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G136" s="11">
+      <c r="F136" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -8681,13 +8530,13 @@
       <c r="C137" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E137" s="8">
+      <c r="D137" s="8">
         <v>57.7</v>
       </c>
-      <c r="F137" s="8" t="s">
+      <c r="E137" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G137" s="11">
+      <c r="F137" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -8701,13 +8550,13 @@
       <c r="C138" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E138" s="8">
+      <c r="D138" s="8">
         <v>51.6</v>
       </c>
-      <c r="F138" s="8" t="s">
+      <c r="E138" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G138" s="11">
+      <c r="F138" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -8721,13 +8570,13 @@
       <c r="C139" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E139" s="8">
+      <c r="D139" s="8">
         <v>53</v>
       </c>
-      <c r="F139" s="8" t="s">
+      <c r="E139" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G139" s="11">
+      <c r="F139" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -8741,21 +8590,21 @@
       <c r="C140" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E140" s="8">
+      <c r="D140" s="8">
         <v>52.1</v>
       </c>
-      <c r="F140" s="8" t="s">
+      <c r="E140" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G140" s="11">
+      <c r="F140" s="11">
         <v>46078</v>
       </c>
       <c r="H140">
-        <f>AVERAGE(E131:E140)</f>
+        <f>AVERAGE(D131:D140)</f>
         <v>53.58</v>
       </c>
       <c r="I140">
-        <f>STDEV(E131:E140)</f>
+        <f>STDEV(D131:D140)</f>
         <v>2.7054677147501796</v>
       </c>
     </row>
@@ -8769,13 +8618,13 @@
       <c r="C141" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E141" s="8">
+      <c r="D141" s="8">
         <v>25.5</v>
       </c>
-      <c r="F141" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G141" s="11">
+      <c r="E141" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F141" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -8789,13 +8638,13 @@
       <c r="C142" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E142" s="8">
+      <c r="D142" s="8">
         <v>24.2</v>
       </c>
-      <c r="F142" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G142" s="11">
+      <c r="E142" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F142" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -8809,13 +8658,13 @@
       <c r="C143" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E143" s="8">
+      <c r="D143" s="8">
         <v>27.3</v>
       </c>
-      <c r="F143" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G143" s="11">
+      <c r="E143" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F143" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -8829,13 +8678,13 @@
       <c r="C144" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E144" s="8">
+      <c r="D144" s="8">
         <v>26.2</v>
       </c>
-      <c r="F144" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G144" s="11">
+      <c r="E144" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F144" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -8849,13 +8698,13 @@
       <c r="C145" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E145" s="8">
+      <c r="D145" s="8">
         <v>25.9</v>
       </c>
-      <c r="F145" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G145" s="11">
+      <c r="E145" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F145" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -8869,13 +8718,13 @@
       <c r="C146" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E146" s="8">
+      <c r="D146" s="8">
         <v>26.2</v>
       </c>
-      <c r="F146" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G146" s="11">
+      <c r="E146" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F146" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -8889,13 +8738,13 @@
       <c r="C147" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E147" s="8">
+      <c r="D147" s="8">
         <v>28</v>
       </c>
-      <c r="F147" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G147" s="11">
+      <c r="E147" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F147" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -8909,13 +8758,13 @@
       <c r="C148" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E148" s="8">
+      <c r="D148" s="8">
         <v>27.4</v>
       </c>
-      <c r="F148" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G148" s="11">
+      <c r="E148" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F148" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -8929,13 +8778,13 @@
       <c r="C149" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E149" s="8">
+      <c r="D149" s="8">
         <v>26</v>
       </c>
-      <c r="F149" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G149" s="11">
+      <c r="E149" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F149" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -8949,21 +8798,21 @@
       <c r="C150" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E150" s="8">
+      <c r="D150" s="8">
         <v>29</v>
       </c>
-      <c r="F150" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G150" s="11">
+      <c r="E150" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F150" s="11">
         <v>46078</v>
       </c>
       <c r="H150">
-        <f>AVERAGE(E141:E150)</f>
+        <f>AVERAGE(D141:D150)</f>
         <v>26.57</v>
       </c>
       <c r="I150">
-        <f>STDEV(E141:E150)</f>
+        <f>STDEV(D141:D150)</f>
         <v>1.3736002976767943</v>
       </c>
     </row>
@@ -8977,13 +8826,13 @@
       <c r="C151" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E151" s="8">
+      <c r="D151" s="8">
         <v>64.7</v>
       </c>
-      <c r="F151" s="8" t="s">
+      <c r="E151" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G151" s="11">
+      <c r="F151" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -8997,13 +8846,13 @@
       <c r="C152" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E152" s="8">
+      <c r="D152" s="8">
         <v>66.2</v>
       </c>
-      <c r="F152" s="8" t="s">
+      <c r="E152" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G152" s="11">
+      <c r="F152" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -9017,13 +8866,13 @@
       <c r="C153" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E153" s="8">
+      <c r="D153" s="8">
         <v>58.8</v>
       </c>
-      <c r="F153" s="8" t="s">
+      <c r="E153" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G153" s="11">
+      <c r="F153" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -9037,13 +8886,13 @@
       <c r="C154" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E154" s="8">
+      <c r="D154" s="8">
         <v>59.3</v>
       </c>
-      <c r="F154" s="8" t="s">
+      <c r="E154" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G154" s="11">
+      <c r="F154" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -9057,13 +8906,13 @@
       <c r="C155" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E155" s="8">
+      <c r="D155" s="8">
         <v>60.8</v>
       </c>
-      <c r="F155" s="8" t="s">
+      <c r="E155" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G155" s="11">
+      <c r="F155" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -9077,13 +8926,13 @@
       <c r="C156" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E156" s="8">
+      <c r="D156" s="8">
         <v>60.4</v>
       </c>
-      <c r="F156" s="8" t="s">
+      <c r="E156" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G156" s="11">
+      <c r="F156" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -9097,13 +8946,13 @@
       <c r="C157" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E157" s="8">
+      <c r="D157" s="8">
         <v>58.6</v>
       </c>
-      <c r="F157" s="8" t="s">
+      <c r="E157" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G157" s="11">
+      <c r="F157" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -9117,13 +8966,13 @@
       <c r="C158" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E158" s="8">
+      <c r="D158" s="8">
         <v>60.9</v>
       </c>
-      <c r="F158" s="8" t="s">
+      <c r="E158" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G158" s="11">
+      <c r="F158" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -9137,13 +8986,13 @@
       <c r="C159" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E159" s="8">
+      <c r="D159" s="8">
         <v>63.6</v>
       </c>
-      <c r="F159" s="8" t="s">
+      <c r="E159" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G159" s="11">
+      <c r="F159" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -9157,21 +9006,21 @@
       <c r="C160" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E160" s="8">
+      <c r="D160" s="8">
         <v>62.9</v>
       </c>
-      <c r="F160" s="8" t="s">
+      <c r="E160" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G160" s="11">
+      <c r="F160" s="11">
         <v>46078</v>
       </c>
       <c r="H160">
-        <f>AVERAGE(E151:E160)</f>
+        <f>AVERAGE(D151:D160)</f>
         <v>61.61999999999999</v>
       </c>
       <c r="I160">
-        <f>STDEV(E151:E160)</f>
+        <f>STDEV(D151:D160)</f>
         <v>2.6067433918802054</v>
       </c>
     </row>
@@ -9185,13 +9034,13 @@
       <c r="C161" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E161" s="8">
+      <c r="D161" s="8">
         <v>30.3</v>
       </c>
-      <c r="F161" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G161" s="11">
+      <c r="E161" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F161" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -9205,13 +9054,13 @@
       <c r="C162" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E162" s="8">
+      <c r="D162" s="8">
         <v>29.5</v>
       </c>
-      <c r="F162" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G162" s="11">
+      <c r="E162" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F162" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -9225,13 +9074,13 @@
       <c r="C163" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E163" s="8">
+      <c r="D163" s="8">
         <v>28.5</v>
       </c>
-      <c r="F163" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G163" s="11">
+      <c r="E163" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F163" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -9245,13 +9094,13 @@
       <c r="C164" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E164" s="8">
+      <c r="D164" s="8">
         <v>25.2</v>
       </c>
-      <c r="F164" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G164" s="11">
+      <c r="E164" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F164" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -9265,13 +9114,13 @@
       <c r="C165" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E165" s="8">
+      <c r="D165" s="8">
         <v>26.4</v>
       </c>
-      <c r="F165" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G165" s="11">
+      <c r="E165" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F165" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -9285,13 +9134,13 @@
       <c r="C166" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E166" s="8">
+      <c r="D166" s="8">
         <v>28.9</v>
       </c>
-      <c r="F166" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G166" s="11">
+      <c r="E166" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F166" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -9305,13 +9154,13 @@
       <c r="C167" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E167" s="8">
+      <c r="D167" s="8">
         <v>28.4</v>
       </c>
-      <c r="F167" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G167" s="11">
+      <c r="E167" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F167" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -9325,13 +9174,13 @@
       <c r="C168" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E168" s="8">
+      <c r="D168" s="8">
         <v>30.2</v>
       </c>
-      <c r="F168" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G168" s="11">
+      <c r="E168" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F168" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -9345,13 +9194,13 @@
       <c r="C169" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E169" s="8">
+      <c r="D169" s="8">
         <v>26.9</v>
       </c>
-      <c r="F169" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G169" s="11">
+      <c r="E169" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F169" s="11">
         <v>46078</v>
       </c>
     </row>
@@ -9365,21 +9214,21 @@
       <c r="C170" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E170" s="8">
+      <c r="D170" s="8">
         <v>27.1</v>
       </c>
-      <c r="F170" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G170" s="11">
+      <c r="E170" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F170" s="11">
         <v>46078</v>
       </c>
       <c r="H170">
-        <f>AVERAGE(E161:E170)</f>
+        <f>AVERAGE(D161:D170)</f>
         <v>28.140000000000004</v>
       </c>
       <c r="I170">
-        <f>STDEV(E161:E170)</f>
+        <f>STDEV(D161:D170)</f>
         <v>1.6939106627367733</v>
       </c>
     </row>
@@ -9393,13 +9242,13 @@
       <c r="C171" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E171" s="8">
+      <c r="D171" s="8">
         <v>68.900000000000006</v>
       </c>
-      <c r="F171" s="8" t="s">
+      <c r="E171" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G171" s="11">
+      <c r="F171" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9413,13 +9262,13 @@
       <c r="C172" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E172" s="8">
+      <c r="D172" s="8">
         <v>66.7</v>
       </c>
-      <c r="F172" s="8" t="s">
+      <c r="E172" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G172" s="11">
+      <c r="F172" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9433,13 +9282,13 @@
       <c r="C173" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E173" s="8">
+      <c r="D173" s="8">
         <v>64.5</v>
       </c>
-      <c r="F173" s="8" t="s">
+      <c r="E173" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G173" s="11">
+      <c r="F173" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9453,13 +9302,13 @@
       <c r="C174" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E174" s="8">
+      <c r="D174" s="8">
         <v>68.099999999999994</v>
       </c>
-      <c r="F174" s="8" t="s">
+      <c r="E174" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G174" s="11">
+      <c r="F174" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9473,13 +9322,13 @@
       <c r="C175" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E175" s="8">
+      <c r="D175" s="8">
         <v>64.099999999999994</v>
       </c>
-      <c r="F175" s="8" t="s">
+      <c r="E175" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G175" s="11">
+      <c r="F175" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9493,13 +9342,13 @@
       <c r="C176" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E176" s="8">
+      <c r="D176" s="8">
         <v>69.7</v>
       </c>
-      <c r="F176" s="8" t="s">
+      <c r="E176" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G176" s="11">
+      <c r="F176" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9513,13 +9362,13 @@
       <c r="C177" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E177" s="8">
+      <c r="D177" s="8">
         <v>66.8</v>
       </c>
-      <c r="F177" s="8" t="s">
+      <c r="E177" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G177" s="11">
+      <c r="F177" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9533,13 +9382,13 @@
       <c r="C178" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E178" s="8">
+      <c r="D178" s="8">
         <v>74.7</v>
       </c>
-      <c r="F178" s="8" t="s">
+      <c r="E178" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G178" s="11">
+      <c r="F178" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9553,13 +9402,13 @@
       <c r="C179" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E179" s="8">
+      <c r="D179" s="8">
         <v>71.5</v>
       </c>
-      <c r="F179" s="8" t="s">
+      <c r="E179" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G179" s="11">
+      <c r="F179" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9573,21 +9422,21 @@
       <c r="C180" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E180" s="8">
+      <c r="D180" s="8">
         <v>73.2</v>
       </c>
-      <c r="F180" s="8" t="s">
+      <c r="E180" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G180" s="11">
+      <c r="F180" s="11">
         <v>46084</v>
       </c>
       <c r="H180">
-        <f>AVERAGE(E171:E180)</f>
+        <f>AVERAGE(D171:D180)</f>
         <v>68.820000000000022</v>
       </c>
       <c r="I180">
-        <f>STDEV(E171:E180)</f>
+        <f>STDEV(D171:D180)</f>
         <v>3.5238236807952448</v>
       </c>
     </row>
@@ -9601,13 +9450,13 @@
       <c r="C181" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E181" s="8">
+      <c r="D181" s="8">
         <v>34.5</v>
       </c>
-      <c r="F181" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G181" s="11">
+      <c r="E181" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F181" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9621,13 +9470,13 @@
       <c r="C182" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E182" s="8">
+      <c r="D182" s="8">
         <v>33.9</v>
       </c>
-      <c r="F182" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G182" s="11">
+      <c r="E182" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F182" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9641,13 +9490,13 @@
       <c r="C183" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E183" s="8">
+      <c r="D183" s="8">
         <v>31.8</v>
       </c>
-      <c r="F183" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G183" s="11">
+      <c r="E183" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F183" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9661,13 +9510,13 @@
       <c r="C184" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E184" s="8">
+      <c r="D184" s="8">
         <v>33.799999999999997</v>
       </c>
-      <c r="F184" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G184" s="11">
+      <c r="E184" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F184" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9681,13 +9530,13 @@
       <c r="C185" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E185" s="8">
+      <c r="D185" s="8">
         <v>35.1</v>
       </c>
-      <c r="F185" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G185" s="11">
+      <c r="E185" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F185" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9701,13 +9550,13 @@
       <c r="C186" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E186" s="8">
+      <c r="D186" s="8">
         <v>33.6</v>
       </c>
-      <c r="F186" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G186" s="11">
+      <c r="E186" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F186" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9721,13 +9570,13 @@
       <c r="C187" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E187" s="8">
+      <c r="D187" s="8">
         <v>33.9</v>
       </c>
-      <c r="F187" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G187" s="11">
+      <c r="E187" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F187" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9741,13 +9590,13 @@
       <c r="C188" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E188" s="8">
+      <c r="D188" s="8">
         <v>33.1</v>
       </c>
-      <c r="F188" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G188" s="11">
+      <c r="E188" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F188" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9761,13 +9610,13 @@
       <c r="C189" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E189" s="8">
+      <c r="D189" s="8">
         <v>34.9</v>
       </c>
-      <c r="F189" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G189" s="11">
+      <c r="E189" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F189" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9781,21 +9630,21 @@
       <c r="C190" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E190" s="8">
+      <c r="D190" s="8">
         <v>33.700000000000003</v>
       </c>
-      <c r="F190" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G190" s="11">
+      <c r="E190" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F190" s="11">
         <v>46084</v>
       </c>
       <c r="H190">
-        <f>AVERAGE(E181:E190)</f>
+        <f>AVERAGE(D181:D190)</f>
         <v>33.83</v>
       </c>
       <c r="I190">
-        <f>STDEV(E181:E190)</f>
+        <f>STDEV(D181:D190)</f>
         <v>0.93932599949822138</v>
       </c>
     </row>
@@ -9809,13 +9658,13 @@
       <c r="C191" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E191" s="8">
+      <c r="D191" s="8">
         <v>58</v>
       </c>
-      <c r="F191" s="8" t="s">
+      <c r="E191" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G191" s="11">
+      <c r="F191" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9829,13 +9678,13 @@
       <c r="C192" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E192" s="8">
+      <c r="D192" s="8">
         <v>52.3</v>
       </c>
-      <c r="F192" s="8" t="s">
+      <c r="E192" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G192" s="11">
+      <c r="F192" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9849,13 +9698,13 @@
       <c r="C193" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E193" s="8">
+      <c r="D193" s="8">
         <v>56.5</v>
       </c>
-      <c r="F193" s="8" t="s">
+      <c r="E193" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G193" s="11">
+      <c r="F193" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9869,13 +9718,13 @@
       <c r="C194" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E194" s="8">
+      <c r="D194" s="8">
         <v>54.6</v>
       </c>
-      <c r="F194" s="8" t="s">
+      <c r="E194" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G194" s="11">
+      <c r="F194" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9889,13 +9738,13 @@
       <c r="C195" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E195" s="8">
+      <c r="D195" s="8">
         <v>54</v>
       </c>
-      <c r="F195" s="8" t="s">
+      <c r="E195" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G195" s="11">
+      <c r="F195" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9909,13 +9758,13 @@
       <c r="C196" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E196" s="8">
+      <c r="D196" s="8">
         <v>59.7</v>
       </c>
-      <c r="F196" s="8" t="s">
+      <c r="E196" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G196" s="11">
+      <c r="F196" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9929,13 +9778,13 @@
       <c r="C197" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E197" s="8">
+      <c r="D197" s="8">
         <v>58.2</v>
       </c>
-      <c r="F197" s="8" t="s">
+      <c r="E197" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G197" s="11">
+      <c r="F197" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9949,13 +9798,13 @@
       <c r="C198" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E198" s="8">
+      <c r="D198" s="8">
         <v>56</v>
       </c>
-      <c r="F198" s="8" t="s">
+      <c r="E198" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G198" s="11">
+      <c r="F198" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9969,13 +9818,13 @@
       <c r="C199" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E199" s="8">
+      <c r="D199" s="8">
         <v>54.2</v>
       </c>
-      <c r="F199" s="8" t="s">
+      <c r="E199" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G199" s="11">
+      <c r="F199" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -9989,21 +9838,21 @@
       <c r="C200" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E200" s="8">
+      <c r="D200" s="8">
         <v>59.9</v>
       </c>
-      <c r="F200" s="8" t="s">
+      <c r="E200" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G200" s="11">
+      <c r="F200" s="11">
         <v>46084</v>
       </c>
       <c r="H200">
-        <f>AVERAGE(E191:E200)</f>
+        <f>AVERAGE(D191:D200)</f>
         <v>56.339999999999996</v>
       </c>
       <c r="I200">
-        <f>STDEV(E191:E200)</f>
+        <f>STDEV(D191:D200)</f>
         <v>2.5760434778939589</v>
       </c>
     </row>
@@ -10017,13 +9866,13 @@
       <c r="C201" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E201" s="8">
+      <c r="D201" s="8">
         <v>29.8</v>
       </c>
-      <c r="F201" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G201" s="11">
+      <c r="E201" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F201" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -10037,13 +9886,13 @@
       <c r="C202" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E202" s="8">
+      <c r="D202" s="8">
         <v>29.4</v>
       </c>
-      <c r="F202" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G202" s="11">
+      <c r="E202" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F202" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -10057,13 +9906,13 @@
       <c r="C203" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E203" s="8">
+      <c r="D203" s="8">
         <v>30.4</v>
       </c>
-      <c r="F203" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G203" s="11">
+      <c r="E203" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F203" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -10077,13 +9926,13 @@
       <c r="C204" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E204" s="8">
+      <c r="D204" s="8">
         <v>36.1</v>
       </c>
-      <c r="F204" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G204" s="11">
+      <c r="E204" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F204" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -10097,13 +9946,13 @@
       <c r="C205" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E205" s="8">
+      <c r="D205" s="8">
         <v>28.3</v>
       </c>
-      <c r="F205" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G205" s="11">
+      <c r="E205" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F205" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -10117,13 +9966,13 @@
       <c r="C206" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E206" s="8">
+      <c r="D206" s="8">
         <v>29.4</v>
       </c>
-      <c r="F206" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G206" s="11">
+      <c r="E206" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F206" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -10137,13 +9986,13 @@
       <c r="C207" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E207" s="8">
+      <c r="D207" s="8">
         <v>28.9</v>
       </c>
-      <c r="F207" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G207" s="11">
+      <c r="E207" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F207" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -10157,13 +10006,13 @@
       <c r="C208" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E208" s="8">
+      <c r="D208" s="8">
         <v>30.1</v>
       </c>
-      <c r="F208" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G208" s="11">
+      <c r="E208" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F208" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -10177,13 +10026,13 @@
       <c r="C209" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E209" s="8">
+      <c r="D209" s="8">
         <v>31.2</v>
       </c>
-      <c r="F209" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G209" s="11">
+      <c r="E209" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F209" s="11">
         <v>46084</v>
       </c>
     </row>
@@ -10197,21 +10046,21 @@
       <c r="C210" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E210" s="8">
+      <c r="D210" s="8">
         <v>32.4</v>
       </c>
-      <c r="F210" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G210" s="11">
+      <c r="E210" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F210" s="11">
         <v>46084</v>
       </c>
       <c r="H210">
-        <f>AVERAGE(E201:E210)</f>
+        <f>AVERAGE(D201:D210)</f>
         <v>30.6</v>
       </c>
       <c r="I210">
-        <f>STDEV(E201:E210)</f>
+        <f>STDEV(D201:D210)</f>
         <v>2.2568414506414349</v>
       </c>
     </row>
@@ -10225,9 +10074,6 @@
       <c r="C211" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D211">
-        <v>0.38</v>
-      </c>
     </row>
     <row r="212" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A212" s="3">
@@ -10239,9 +10085,6 @@
       <c r="C212" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D212">
-        <v>0.36</v>
-      </c>
     </row>
     <row r="213" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A213" s="3">
@@ -10253,9 +10096,6 @@
       <c r="C213" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D213">
-        <v>0.37</v>
-      </c>
     </row>
     <row r="214" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A214" s="3">
@@ -10267,9 +10107,6 @@
       <c r="C214" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D214">
-        <v>0.38</v>
-      </c>
     </row>
     <row r="215" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A215" s="3">
@@ -10280,9 +10117,6 @@
       </c>
       <c r="C215" s="13" t="s">
         <v>22</v>
-      </c>
-      <c r="D215">
-        <v>0.37</v>
       </c>
     </row>
     <row r="216" spans="1:11" ht="17" x14ac:dyDescent="0.2">
@@ -10295,9 +10129,6 @@
       <c r="C216" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D216">
-        <v>0.37</v>
-      </c>
     </row>
     <row r="217" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A217" s="3">
@@ -10309,9 +10140,6 @@
       <c r="C217" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D217">
-        <v>0.37</v>
-      </c>
     </row>
     <row r="218" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A218" s="3">
@@ -10323,9 +10151,6 @@
       <c r="C218" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D218">
-        <v>0.36</v>
-      </c>
     </row>
     <row r="219" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A219" s="3">
@@ -10337,16 +10162,13 @@
       <c r="C219" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D219">
-        <v>0.37</v>
-      </c>
-      <c r="J219">
+      <c r="J219" t="e">
         <f>AVERAGE(D211:D220)</f>
-        <v>0.36899999999999999</v>
-      </c>
-      <c r="K219">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K219" t="e">
         <f>STDEV(D211:D220)</f>
-        <v>7.3786478737262262E-3</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="220" spans="1:11" ht="17" x14ac:dyDescent="0.2">
@@ -10359,9 +10181,6 @@
       <c r="C220" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D220">
-        <v>0.36</v>
-      </c>
     </row>
     <row r="221" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A221" s="3">
@@ -10373,9 +10192,6 @@
       <c r="C221" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D221">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="222" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A222" s="3">
@@ -10387,9 +10203,6 @@
       <c r="C222" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D222">
-        <v>0.41</v>
-      </c>
     </row>
     <row r="223" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A223" s="3">
@@ -10401,9 +10214,6 @@
       <c r="C223" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D223">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="224" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A224" s="3">
@@ -10415,9 +10225,6 @@
       <c r="C224" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D224">
-        <v>0.41</v>
-      </c>
     </row>
     <row r="225" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A225" s="3">
@@ -10428,9 +10235,6 @@
       </c>
       <c r="C225" s="13" t="s">
         <v>22</v>
-      </c>
-      <c r="D225">
-        <v>0.41</v>
       </c>
     </row>
     <row r="226" spans="1:11" ht="17" x14ac:dyDescent="0.2">
@@ -10443,9 +10247,6 @@
       <c r="C226" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D226">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="227" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A227" s="3">
@@ -10457,9 +10258,6 @@
       <c r="C227" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D227">
-        <v>0.41</v>
-      </c>
     </row>
     <row r="228" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A228" s="3">
@@ -10471,9 +10269,6 @@
       <c r="C228" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D228">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="229" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A229" s="3">
@@ -10485,9 +10280,6 @@
       <c r="C229" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D229">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="230" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A230" s="3">
@@ -10499,16 +10291,13 @@
       <c r="C230" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D230">
-        <v>0.42</v>
-      </c>
-      <c r="J230">
+      <c r="J230" t="e">
         <f>AVERAGE(D221:D230)</f>
-        <v>0.40599999999999997</v>
-      </c>
-      <c r="K230">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K230" t="e">
         <f>STDEV(D221:D230)</f>
-        <v>6.9920589878009901E-3</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
